--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487017_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487017_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.052</v>
+        <v>1.3658</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3099</v>
+        <v>0.6237</v>
       </c>
       <c r="F2" t="n">
         <v>0.7421</v>
@@ -610,10 +610,10 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8368</v>
+        <v>-0.523</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0464</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0455</v>
+        <v>0.4117</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1562</v>
+        <v>1.7086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2016</v>
+        <v>-1.297</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1679</v>
+        <v>1.2121</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5187</v>
+        <v>-0.1164</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6866</v>
+        <v>1.3284</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2452</v>
+        <v>2.584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3733</v>
+        <v>1.0717</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.5124</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.372</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1455</v>
+        <v>-1.188</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0682</v>
+        <v>-0.1839</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3723</v>
+        <v>-0.4291</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1513</v>
+        <v>0.1083</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.221</v>
+        <v>-0.5374</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2357</v>
+        <v>0.2447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2402</v>
+        <v>1.0698</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.476</v>
+        <v>-0.825</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VENTURA PEDREÑO</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2589</v>
+        <v>0.2522</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0732</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3322</v>
+        <v>0.172</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1547</v>
+        <v>-0.1679</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4834</v>
+        <v>0.5187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3288</v>
+        <v>-0.6866</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4685</v>
+        <v>-0.2452</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3504</v>
+        <v>0.3733</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1181</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6231</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8338</v>
+        <v>0.1455</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7893</v>
+        <v>-0.0682</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3096</v>
+        <v>-0.1656</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3952</v>
+        <v>0.0851</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0856</v>
+        <v>-0.2507</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2357</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>A. VENTURA PEDREÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5164</v>
+        <v>0.0458</v>
       </c>
       <c r="E5" t="n">
-        <v>0.988</v>
+        <v>1.3483</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5045</v>
+        <v>-1.3025</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2121</v>
+        <v>-0.1547</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1164</v>
+        <v>-0.4834</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3284</v>
+        <v>0.3288</v>
       </c>
       <c r="J5" t="n">
-        <v>2.584</v>
+        <v>1.4685</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0717</v>
+        <v>0.3504</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5124</v>
+        <v>1.1181</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.372</v>
+        <v>-1.6231</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.188</v>
+        <v>-0.8338</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1839</v>
+        <v>-0.7893</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3572</v>
+        <v>-0.0049</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.1202</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7448</v>
+        <v>0.1153</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2447</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4763</v>
+        <v>-1.8782</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3205</v>
+        <v>-0.7468</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1557</v>
+        <v>-1.1314</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2006</v>
+        <v>-0.6868</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.5345</v>
+        <v>-0.0002</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3339</v>
+        <v>-0.6866</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5574</v>
+        <v>0.7992</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.1227</v>
+        <v>0.7202</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5653</v>
+        <v>0.0789</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6432</v>
+        <v>-1.486</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4118</v>
+        <v>-0.7204</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7685999999999999</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.157</v>
+        <v>0.4513</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1117</v>
+        <v>0.5075</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2687</v>
+        <v>-0.0561</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7027</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.117</v>
+        <v>-2.1879</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3752</v>
+        <v>0.2756</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7418</v>
+        <v>-2.4635</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3236</v>
+        <v>0.7496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.668</v>
+        <v>-0.1818</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3445</v>
+        <v>0.9315</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6985</v>
+        <v>2.2012</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5801</v>
+        <v>1.5962</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1184</v>
+        <v>0.605</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.375</v>
+        <v>-1.4516</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9121</v>
+        <v>-1.778</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4629</v>
+        <v>0.3264</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2321</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.437</v>
+        <v>-0.3215</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6778</v>
+        <v>0.1278</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2408</v>
+        <v>-0.4493</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6456</v>
+        <v>-1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9474</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5924</v>
+        <v>-2.1879</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2474</v>
+        <v>-0.3868</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3449</v>
+        <v>-1.8011</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7496</v>
+        <v>0.3236</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1818</v>
+        <v>0.668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9315</v>
+        <v>-0.3445</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2012</v>
+        <v>1.6985</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5962</v>
+        <v>1.5801</v>
       </c>
       <c r="L8" t="n">
-        <v>0.605</v>
+        <v>0.1184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4516</v>
+        <v>-1.375</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.778</v>
+        <v>-0.9121</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3264</v>
+        <v>-0.4629</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4374</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.726</v>
+        <v>0.3662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3952</v>
+        <v>0.6662</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3307</v>
+        <v>-0.3001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>-1.6456</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-0.9474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8012</v>
+        <v>-2.2423</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3777</v>
+        <v>-1.2348</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4235</v>
+        <v>-1.0075</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2335</v>
+        <v>-1.2006</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8783</v>
+        <v>-4.5345</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3552</v>
+        <v>3.3339</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2579</v>
+        <v>-0.5574</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6</v>
+        <v>-3.1227</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6579</v>
+        <v>2.5653</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9756</v>
+        <v>-0.6432</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2783</v>
+        <v>-1.4118</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3027</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6427</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.726</v>
+        <v>-0.923</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9336</v>
+        <v>0.1974</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2076</v>
+        <v>-1.1204</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3491</v>
+        <v>0.7027</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3491</v>
+        <v>-0.476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8929</v>
+        <v>-3.2444</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5836</v>
+        <v>-2.9395</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3093</v>
+        <v>-0.3049</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6868</v>
+        <v>-2.2335</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0002</v>
+        <v>-1.8783</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6866</v>
+        <v>-0.3552</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7992</v>
+        <v>-1.2579</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7202</v>
+        <v>-0.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0789</v>
+        <v>-0.6579</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.486</v>
+        <v>-0.9756</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7204</v>
+        <v>-1.2783</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="P10" t="n">
         <v>-1.6427</v>
@@ -1234,28 +1234,28 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5633</v>
+        <v>0.2828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3294</v>
+        <v>0.3719</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.234</v>
+        <v>-0.0891</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ROKER</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.934</v>
+        <v>-3.9205</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.78</v>
+        <v>-0.6803</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.154</v>
+        <v>-3.2402</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2972</v>
+        <v>-2.6677</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7421</v>
+        <v>-1.1258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4448</v>
+        <v>-1.5418</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2641</v>
+        <v>-0.4244</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3825</v>
+        <v>0.2599</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1184</v>
+        <v>-0.6843</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0332</v>
+        <v>-2.2432</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3596</v>
+        <v>-1.3857</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3264</v>
+        <v>-0.8575</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2409</v>
+        <v>0.2141</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2357</v>
+        <v>0.5306</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0052</v>
+        <v>-0.3166</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6456</v>
+        <v>-1.0563</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9474</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>A. ROKER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2698</v>
+        <v>-4.1875</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2963</v>
+        <v>-2.826</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9735</v>
+        <v>-1.3615</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6677</v>
+        <v>-1.2972</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1258</v>
+        <v>-1.7421</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5418</v>
+        <v>0.4448</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4244</v>
+        <v>-0.2641</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2599</v>
+        <v>-0.3825</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6843</v>
+        <v>0.1184</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2432</v>
+        <v>-1.0332</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3857</v>
+        <v>-1.3596</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8575</v>
+        <v>0.3264</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1352</v>
+        <v>-0.0126</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0854</v>
+        <v>0.1897</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0498</v>
+        <v>-0.2023</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0563</v>
+        <v>-1.6456</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2402</v>
+        <v>-0.6982</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2965</v>
+        <v>-0.9474</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.7614</v>
+        <v>-17.7732</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7658</v>
+        <v>-4.777799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.9957</v>
+        <v>-12.9955</v>
       </c>
       <c r="G13" t="n">
         <v>-5.418299999999999</v>
@@ -1438,13 +1438,13 @@
         <v>-8.207800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7895</v>
+        <v>2.789499999999999</v>
       </c>
       <c r="J13" t="n">
         <v>6.622299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.150800000000001</v>
+        <v>3.1508</v>
       </c>
       <c r="L13" t="n">
         <v>3.4716</v>
@@ -1468,13 +1468,13 @@
         <v>8.213800000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0535</v>
+        <v>-1.0653</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1994</v>
+        <v>2.1876</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.253</v>
+        <v>-3.2531</v>
       </c>
       <c r="V13" t="n">
         <v>-4.1027</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.365500000000001</v>
+        <v>6.8871</v>
       </c>
       <c r="E14" t="n">
-        <v>6.182</v>
+        <v>4.8221</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1835</v>
+        <v>2.065</v>
       </c>
       <c r="G14" t="n">
         <v>4.3098</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>1.645</v>
+        <v>0.1666</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7355</v>
+        <v>0.3756</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.209</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2271</v>
+        <v>6.0482</v>
       </c>
       <c r="E15" t="n">
-        <v>4.189</v>
+        <v>4.9212</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0381</v>
+        <v>1.127</v>
       </c>
       <c r="G15" t="n">
         <v>4.4846</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7853</v>
+        <v>0.0359</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7827</v>
+        <v>-0.0505</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0025</v>
+        <v>0.0864</v>
       </c>
       <c r="V15" t="n">
         <v>1.5277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8228</v>
+        <v>5.3633</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5533</v>
+        <v>3.6579</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2695</v>
+        <v>1.7054</v>
       </c>
       <c r="G16" t="n">
         <v>1.8667</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2867</v>
+        <v>0.8272</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6933</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4066</v>
+        <v>0.0293</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8332</v>
+        <v>4.2333</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4318</v>
+        <v>2.2686</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4014</v>
+        <v>1.9646</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4779</v>
@@ -1780,13 +1780,13 @@
         <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1468</v>
+        <v>-0.7468</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9804</v>
+        <v>-0.1435</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1664</v>
+        <v>-0.6032</v>
       </c>
       <c r="V17" t="n">
         <v>3.4045</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2559</v>
+        <v>1.6512</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0172</v>
+        <v>1.1282</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2386</v>
+        <v>0.523</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4433</v>
+        <v>1.6154</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6329</v>
+        <v>-0.0712</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8104</v>
+        <v>1.6867</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4393</v>
+        <v>2.4302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1397</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.579</v>
+        <v>1.8944</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0041</v>
+        <v>-0.8147</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7726</v>
+        <v>-0.6071</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2314</v>
+        <v>-0.2077</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2618</v>
+        <v>0.4813</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4565</v>
+        <v>0.5112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1947</v>
+        <v>-0.0299</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7812</v>
+        <v>0.4696</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6052</v>
+        <v>0.1804</v>
       </c>
       <c r="F19" t="n">
-        <v>0.176</v>
+        <v>0.2892</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6154</v>
+        <v>-1.4433</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0712</v>
+        <v>-0.6329</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6867</v>
+        <v>-0.8104</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4302</v>
+        <v>-0.4393</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.1397</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8944</v>
+        <v>-0.579</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8147</v>
+        <v>-1.0041</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6071</v>
+        <v>-0.7726</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2077</v>
+        <v>-0.2314</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3886</v>
+        <v>0.4755</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0118</v>
+        <v>0.6197</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3769</v>
+        <v>-0.1442</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2299</v>
+        <v>0.035</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5585</v>
+        <v>-0.7217</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3286</v>
+        <v>0.7567</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7667</v>
@@ -2014,13 +2014,13 @@
         <v>2.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1409</v>
+        <v>0.124</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6355</v>
+        <v>0.2013</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4947</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.2402</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>A. BUTKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4376</v>
+        <v>-0.7117</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8531</v>
+        <v>-0.581</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2907</v>
+        <v>-0.1307</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5332</v>
+        <v>-0.8531</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3175</v>
+        <v>-0.8531</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2157</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3362</v>
+        <v>-0.6584</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3756</v>
+        <v>-0.6584</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.197</v>
+        <v>-0.1947</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0582</v>
+        <v>-0.1947</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2552</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4796</v>
+        <v>0.1763</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9758</v>
+        <v>0.0775</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5038</v>
+        <v>0.0988</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7679</v>
+        <v>-0.2402</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0082</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BUTKO</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9802</v>
+        <v>-1.7452</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7902</v>
+        <v>-0.2975</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.19</v>
+        <v>-1.4477</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8531</v>
+        <v>-0.5332</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8531</v>
+        <v>-0.3175</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.2157</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6584</v>
+        <v>-0.3362</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6584</v>
+        <v>-0.3756</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1947</v>
+        <v>-0.197</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1947</v>
+        <v>0.0582</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.2552</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0922</v>
+        <v>1.172</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1317</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0395</v>
+        <v>0.3468</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2402</v>
+        <v>-1.7679</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2402</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8766</v>
+        <v>-2.772</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4873</v>
+        <v>-2.3827</v>
       </c>
       <c r="F23" t="n">
         <v>-0.3893</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.7614</v>
+        <v>19.4588</v>
       </c>
       <c r="E24" t="n">
-        <v>12.9956</v>
+        <v>12.9955</v>
       </c>
       <c r="F24" t="n">
-        <v>5.765699999999999</v>
+        <v>6.463200000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>5.418299999999999</v>
+        <v>5.4183</v>
       </c>
       <c r="H24" t="n">
-        <v>8.207800000000001</v>
+        <v>8.207799999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-2.7893</v>
@@ -2305,7 +2305,7 @@
         <v>11.3585</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6822000000000001</v>
+        <v>0.6821999999999997</v>
       </c>
       <c r="M24" t="n">
         <v>-6.622399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>15.4006</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0534</v>
+        <v>2.7507</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2531</v>
+        <v>3.253</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1995</v>
+        <v>-0.5023</v>
       </c>
       <c r="V24" t="n">
         <v>4.1027</v>
